--- a/src/main/resources/templates/AttendanceApply_add_Template.xlsx
+++ b/src/main/resources/templates/AttendanceApply_add_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\WorkSpace\New_HR\HR-11-codex\src\main\resources\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Java\WorkSpace\New_HR\HAE-VHR\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64276A6-01E5-4AAB-BA14-F7ADD0B80D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F56709CD-AC9F-47B4-9421-2598CA3FC49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9195" yWindow="1350" windowWidth="29010" windowHeight="15150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -133,7 +133,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -143,6 +143,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="51"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -202,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -220,6 +226,10 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,7 +530,7 @@
       <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -544,7 +554,7 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="3" t="str">
+      <c r="E2" s="8" t="str">
         <f>IF(D2="","",VLOOKUP(D2,TemplateCode!A:B,2,0))</f>
         <v/>
       </c>
@@ -559,7 +569,7 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="3" t="str">
+      <c r="E3" s="8" t="str">
         <f>IF(D3="","",VLOOKUP(D3,TemplateCode!A:B,2,0))</f>
         <v/>
       </c>
@@ -574,7 +584,7 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="3" t="str">
+      <c r="E4" s="8" t="str">
         <f>IF(D4="","",VLOOKUP(D4,TemplateCode!A:B,2,0))</f>
         <v/>
       </c>
@@ -589,7 +599,7 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="3" t="str">
+      <c r="E5" s="8" t="str">
         <f>IF(D5="","",VLOOKUP(D5,TemplateCode!A:B,2,0))</f>
         <v/>
       </c>
@@ -604,7 +614,7 @@
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="3" t="str">
+      <c r="E6" s="8" t="str">
         <f>IF(D6="","",VLOOKUP(D6,TemplateCode!A:B,2,0))</f>
         <v/>
       </c>
@@ -619,7 +629,7 @@
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="3" t="str">
+      <c r="E7" s="8" t="str">
         <f>IF(D7="","",VLOOKUP(D7,TemplateCode!A:B,2,0))</f>
         <v/>
       </c>
@@ -634,7 +644,7 @@
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="3" t="str">
+      <c r="E8" s="8" t="str">
         <f>IF(D8="","",VLOOKUP(D8,TemplateCode!A:B,2,0))</f>
         <v/>
       </c>
